--- a/docs/chapter4-figures/chapter4-data.xlsx
+++ b/docs/chapter4-figures/chapter4-data.xlsx
@@ -7,14 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="خوشه‌بندی_k" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="اندازه_خوشه‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="وزن_AHP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="وزن_پایه_تطبیقی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="VIKOR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TOPSIS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="COPRAS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="رتبه‌بندی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="نمودار۴-۱" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="نمودار۴-۲" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="نمودار۴-۳" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="نمودار۴-۴" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="نمودار۴-۵" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="نمودار۴-۶" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="نمودار۴-۷" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="نمودار۴-۸" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="نمودار۴-۹" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="نمودار۴-۹ب" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="نمودار۴-۱۰" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="نمودار۴-۱۱" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="نمودار۴-۱۲" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,13 +29,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,8 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -129,6 +145,1873 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Inertia &amp; Silhouette</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱'!$B$4:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱'!$C$4:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>VIKOR — شاخص نهایی Q</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۹ب'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۹ب'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۹ب'!$B$4:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۹ب'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۹ب'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۹ب'!$C$4:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>COPRAS</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱۰'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱۰'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱۰'!$B$4:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱۰'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱۰'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱۰'!$C$4:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>مقایسه رتبه</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱۱'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱۱'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱۱'!$B$4:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱۱'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱۱'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱۱'!$C$4:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱۱'!D3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱۱'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱۱'!$D$4:$D$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>همبستگی اسپیرمن</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱۲'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱۲'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱۲'!$B$4:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۱۲'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۱۲'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۱۲'!$C$4:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Inertia (WCSS)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۲'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۲'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۲'!$B$4:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۲'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۲'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۲'!$C$4:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Inertia</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Silhouette</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۳'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۳'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۳'!$B$4:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۳'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۳'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۳'!$C$4:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>ضریب</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>تعداد اعضای خوشه</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۴'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۴'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۴'!$B$4:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۴'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۴'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۴'!$C$4:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>وزن معیارها (AHP)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۵'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۵'!$A$4:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۵'!$B$4:$B$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>سهم (%)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>مقایسه وزن‌ها</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۶'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۶'!$A$4:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۶'!$B$4:$B$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۶'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۶'!$A$4:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۶'!$C$4:$C$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>وزن</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>وزن تطبیقی</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۷'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۷'!$A$4:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۷'!$B$4:$B$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>سهم (%)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>TOPSIS — ضریب نزدیکی</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۸'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۸'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۸'!$B$4:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۸'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۸'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۸'!$C$4:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>VIKOR — شاخص‌ها</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۹'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۹'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۹'!$B$4:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۹'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۹'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۹'!$C$4:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'نمودار۴-۹'!D3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'نمودار۴-۹'!$A$4:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'نمودار۴-۹'!$D$4:$D$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -420,83 +2303,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۱ — تغییرات شاخص Inertia و Silhouette برحسب تعداد خوشه‌ها</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Inertia</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Silhouette</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="n">
-        <v>55.958</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="n">
-        <v>34.293</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.323</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.725</v>
+        <v>55.958</v>
       </c>
       <c r="C4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.242</v>
+        <v>34.293</v>
       </c>
       <c r="C5" t="n">
-        <v>0.404</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>23.725</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>14.242</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.404</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
+      <c r="B8" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۹ — مقایسه فناوری‌ها بر اساس شاخص نهایی روش VIKOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>فناوری</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Q_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LoRaWAN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.793</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sigfox</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NB-IoT</t>
+        </is>
+      </c>
       <c r="B6" t="n">
-        <v>10.81</v>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۱۰ — مقایسه فناوری‌ها بر اساس روش COPRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>فناوری</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Q_i</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>N_i (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LoRaWAN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sigfox</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="C5" t="n">
+        <v>81.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NB-IoT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1783</v>
       </c>
       <c r="C6" t="n">
-        <v>0.485</v>
+        <v>39.3</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۱۱ — مقایسه رتبه فناوری‌ها در روش‌های TOPSIS، VIKOR و COPRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>فناوری</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TOPSIS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>VIKOR</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>COPRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LoRaWAN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sigfox</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NB-IoT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۱۲ — ضریب همبستگی رتبه‌ای اسپیرمن بین روش‌های تصمیم‌گیری</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>جفت روش‌ها</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ضریب اسپیرمن</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOPSIS — و VIKOR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TOPSIS — و COPRAS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VIKOR — و COPRAS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -506,78 +2740,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>خوشه</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>تعداد</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>خوشه ۰
-Long-Range LPWAN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۲ — تغییرات Inertia در مقادیر مختلف k</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Inertia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>55.958</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>خوشه ۱
-High-Throughput WLAN</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>خوشه ۲
-Short-Range PAN</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>خوشه ۳
-Extended-Range</t>
-        </is>
-      </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>34.293</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>خوشه ۴
-Cellular IoT</t>
-        </is>
+      <c r="A6" t="n">
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>23.725</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>14.242</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>10.81</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -587,103 +2823,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>معیار</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>سهم_%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>تأخیر رفت‌وبرگشتی</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8.66</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۳ — تغییرات ضریب Silhouette در مقادیر مختلف k</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>وابستگی سلولی</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>9.880000000000001</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Silhouette</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>نرخ داده</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.08</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>بودجه لینک</t>
-        </is>
+      <c r="A5" t="n">
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.07</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>مصرف انرژی</t>
-        </is>
+      <c r="A6" t="n">
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.59</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>برد انتقال</t>
-        </is>
+      <c r="A7" t="n">
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.05</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>هزینه بهره‌برداری سالانه</t>
-        </is>
+      <c r="A8" t="n">
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.74</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>هزینه اولیه سخت‌افزار</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>16.92</v>
+        <v>0.485</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -693,132 +2906,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>معیار</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>پایه</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>تطبیقی</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>تأخیر</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.0866</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0164</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۴ — تعداد اعضای هر خوشه در ساختار نهایی خوشه‌بندی</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>مصرف انرژی</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.1259</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0238</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>خوشه</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>تعداد اعضا</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>نرخ داده</t>
+          <t>خوشه ۰ — Long-Range LPWAN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1108</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0345</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>بودجه لینک</t>
+          <t>خوشه ۱ — High-Throughput WLAN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1207</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.062</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>هزینه سخت‌افزار</t>
+          <t>خوشه ۲ — Short-Range PAN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1692</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.08690000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>برد انتقال</t>
+          <t>خوشه ۳ — Extended-Range</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1305</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.1821</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>هزینه بهره‌برداری</t>
+          <t>خوشه ۴ — Cellular IoT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1574</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.2197</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>وابستگی سلولی</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0988</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.3747</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -828,81 +2999,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>فناوری</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LoRaWAN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.3591</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.1821</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.793</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۵ — وزن نهایی معیارهای تصمیم‌گیری بر اساس روش AHP</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sigfox</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.2706</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.2197</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.975</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>معیار</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>سهم (%)</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NB-IoT</t>
+          <t>تأخیر رفت‌وبرگشتی</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8289</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.3747</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>وابستگی سلولی</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9.880000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>نرخ داده</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>بودجه لینک</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12.07</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>مصرف انرژی</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12.59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>برد انتقال</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>هزینه بهره‌برداری سالانه</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>15.74</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>هزینه اولیه سخت‌افزار</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16.92</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -912,53 +3122,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>فناوری</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ضریب_نزدیکی</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LoRaWAN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.885</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۶ — مقایسه وزن پایه و وزن تطبیقی معیارهای تصمیم‌گیری</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sigfox</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.821</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>معیار</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>وزن پایه AHP</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>وزن تطبیقی</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NB-IoT</t>
+          <t>تأخیر</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0977</v>
+        <v>0.0866</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0164</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>مصرف انرژی</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0238</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>نرخ داده</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0345</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>بودجه لینک</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>هزینه سخت‌افزار</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08690000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>برد انتقال</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1821</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>هزینه بهره‌برداری</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2197</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>وابستگی سلولی</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3747</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -968,67 +3274,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>فناوری</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LoRaWAN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.4535</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۷ — وزن تطبیقی معیارها در سناریوی اصلی</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sigfox</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.3681</v>
-      </c>
-      <c r="C3" t="n">
-        <v>81.2</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>معیار</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>سهم (%)</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NB-IoT</t>
+          <t>تأخیر رفت‌وبرگشتی</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1783</v>
-      </c>
-      <c r="C4" t="n">
-        <v>39.3</v>
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>مصرف انرژی</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>نرخ داده</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>بودجه لینک</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>هزینه سخت‌افزار</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>برد انتقال</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18.21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>هزینه بهره‌برداری سالانه</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>21.97</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>وابستگی سلولی</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>37.47</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1038,80 +3397,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۸ — مقایسه ضریب نزدیکی فناوری‌ها در روش TOPSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>فناوری</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>TOPSIS</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VIKOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>COPRAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LoRaWAN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sigfox</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ضریب نزدیکی (C_i)</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>LoRaWAN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sigfox</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.821</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>NB-IoT</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>0.0977</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نمودار ۴-۹ — مقایسه فناوری‌ها بر اساس شاخص‌های روش VIKOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>فناوری</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>S_i</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>R_i</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Q_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LoRaWAN</t>
+        </is>
+      </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>0.3591</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0.1821</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0.793</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sigfox</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NB-IoT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8289</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/chapter4-figures/chapter4-data.xlsx
+++ b/docs/chapter4-figures/chapter4-data.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
   <si>
     <t>نمودار ۴-۱ — تغییرات شاخص Inertia و Silhouette برحسب تعداد خوشه‌ها</t>
   </si>
@@ -160,7 +160,16 @@
     <t>نمودار ۴-۱۰ — مقایسه فناوری‌ها بر اساس روش COPRAS</t>
   </si>
   <si>
-    <t>N_i</t>
+    <t>اهمیت نسبی (Q_i)</t>
+  </si>
+  <si>
+    <t>درجه مطلوبیت (N_i)</t>
+  </si>
+  <si>
+    <t>مجموع سود (S_i+)</t>
+  </si>
+  <si>
+    <t>مجموع هزینه (S_i-)</t>
   </si>
   <si>
     <t>نمودار ۴-۱۱ — مقایسه رتبه فناوری‌ها در روش‌های TOPSIS، VIKOR و COPRAS</t>
@@ -646,14 +655,11 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Q_i</c:v>
+                  <c:v>اهمیت نسبی (Q_i)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:dLbls>
-            <c:showVal val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'نمودار۴-۱۰'!$A$4:$A$6</c:f>
@@ -695,18 +701,136 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
+              <c:f>'نمودار۴-۱۰'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>مجموع سود (S_i+)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'نمودار۴-۱۰'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>LoRaWAN</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sigfox</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NB-IoT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'نمودار۴-۱۰'!$D$4:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.08069999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0892</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1087</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'نمودار۴-۱۰'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>مجموع هزینه (S_i-)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'نمودار۴-۱۰'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>LoRaWAN</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sigfox</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NB-IoT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'نمودار۴-۱۰'!$E$4:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.09379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1254</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50110001"/>
+        <c:axId val="50110002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="straight_with_markers"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
               <c:f>'نمودار۴-۱۰'!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>N_i</c:v>
+                  <c:v>درجه مطلوبیت (N_i)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:dLbls>
-            <c:showVal val="1"/>
-          </c:dLbls>
+          <c:spPr>
+            <a:ln w="31750">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
           <c:cat>
             <c:strRef>
               <c:f>'نمودار۴-۱۰'!$A$4:$A$6</c:f>
@@ -743,15 +867,34 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="50110001"/>
-        <c:axId val="50110002"/>
-      </c:barChart>
+        <c:marker val="1"/>
+        <c:axId val="60110001"/>
+        <c:axId val="60110002"/>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="50110001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>فناوری</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50110002"/>
         <c:crosses val="autoZero"/>
@@ -763,18 +906,84 @@
         <c:axId val="50110002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="0.7"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Q_i / S_i</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50110001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:valAx>
+        <c:axId val="60110002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="120"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>N_i (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="60110001"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="60110001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="60110002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -2572,15 +2781,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3388,33 +3597,40 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
-    <col min="2" max="3" width="14.7109375" customWidth="1"/>
+    <col min="2" max="5" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="36" customHeight="1">
+    <row r="1" spans="1:5" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>45</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -3424,8 +3640,14 @@
       <c r="C4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>0.08069999999999999</v>
+      </c>
+      <c r="E4">
+        <v>0.09379999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -3435,8 +3657,14 @@
       <c r="C5">
         <v>81.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <v>0.0892</v>
+      </c>
+      <c r="E5">
+        <v>0.1254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -3446,10 +3674,16 @@
       <c r="C6">
         <v>39.3</v>
       </c>
+      <c r="D6">
+        <v>0.1087</v>
+      </c>
+      <c r="E6">
+        <v>0.5023</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3467,7 +3701,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3478,13 +3712,13 @@
         <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3549,7 +3783,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3557,15 +3791,15 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3573,7 +3807,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3581,7 +3815,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>1</v>
